--- a/artfynd/A 46157-2024 artfynd.xlsx
+++ b/artfynd/A 46157-2024 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3040675</v>
+        <v>725044</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klaragylet, 150 m O, Bl</t>
+          <t>150 m O Vitagyl, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468763.6685757249</v>
+        <v>468764</v>
       </c>
       <c r="R2" t="n">
-        <v>6251129.873994377</v>
+        <v>6251130</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,38 +738,23 @@
           <t>Kyrkhult</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>K-Olo-0179</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-04-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-04-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Skogen avverkad</t>
+          <t>Allm</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -782,6 +762,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -793,61 +778,52 @@
           <t>Ivar Björegren</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>725044</v>
+        <v>131494012</v>
       </c>
       <c r="B3" t="n">
-        <v>93053</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>150 m O Vitagyl, Bl</t>
+          <t>Klaragylet, 150 m O, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468763.6685757249</v>
+        <v>468764</v>
       </c>
       <c r="R3" t="n">
-        <v>6251129.873994377</v>
+        <v>6251130</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,29 +845,24 @@
           <t>Kyrkhult</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>K-Olo-0179</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-09-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-09-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-04-30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Allm</t>
+          <t>Ett par plantor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,23 +874,22 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Ivar Björegren</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Ivar Björegren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46157-2024 artfynd.xlsx
+++ b/artfynd/A 46157-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/725044</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,8 +900,17 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131494012</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>